--- a/Timetables.xlsx
+++ b/Timetables.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30524"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://officenationalstatistics-my.sharepoint.com/personal/craig_parkinson_ons_gov_uk/Documents/Documents/Projects/ONS Data Science Network/2026 Conference/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\parkic\src\Data-Sci-Eng-agenda\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="243" documentId="8_{692D790B-6EE5-4A5F-A917-F8C6069EF07E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E941B58C-7571-45C5-A8C4-FC656B68651F}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{576AE2FA-A46C-4C22-B29F-8D2D5487ACB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-94" yWindow="26" windowWidth="25594" windowHeight="17888" xr2:uid="{A0A79721-EAFF-4044-AEE2-C7FE2A8DFDF6}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{A0A79721-EAFF-4044-AEE2-C7FE2A8DFDF6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="52">
   <si>
     <t>Timeslot</t>
   </si>
@@ -202,9 +202,6 @@
     <t>Anne Griffiths - IABS processing</t>
   </si>
   <si>
-    <t>Dan Harris</t>
-  </si>
-  <si>
     <t>14:50 - 15:00</t>
   </si>
   <si>
@@ -215,9 +212,6 @@
   </si>
   <si>
     <t>Dan Shiloh - Bad requirements</t>
-  </si>
-  <si>
-    <t>Matt Wray</t>
   </si>
   <si>
     <t>15:10 - 15:20</t>
@@ -245,7 +239,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -601,8 +595,68 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -615,66 +669,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1010,8 +1004,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E534438A-ACBE-488F-A7ED-B955183CFDB8}">
-  <dimension ref="A1:G24"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:G25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
     <col min="2" max="2" width="33.5546875" customWidth="1"/>
@@ -1020,303 +1014,305 @@
     <col min="5" max="5" width="14.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="16.5" thickBot="1">
+    <row r="1" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="21" t="s">
+      <c r="C1" s="41" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="22"/>
+      <c r="D1" s="42"/>
       <c r="E1" s="19" t="s">
         <v>3</v>
       </c>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="30" t="s">
+      <c r="B2" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="40" t="s">
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="22" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="15.75">
+    <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="32"/>
-      <c r="C3" s="33"/>
-      <c r="D3" s="33"/>
-      <c r="E3" s="41"/>
+      <c r="B3" s="33"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="23"/>
       <c r="F3" s="1"/>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="34"/>
-      <c r="C4" s="35"/>
-      <c r="D4" s="35"/>
-      <c r="E4" s="41"/>
-    </row>
-    <row r="5" spans="1:7">
+      <c r="B4" s="35"/>
+      <c r="C4" s="36"/>
+      <c r="D4" s="36"/>
+      <c r="E4" s="23"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="36" t="s">
+      <c r="B5" s="37" t="s">
         <v>10</v>
       </c>
       <c r="C5" s="17"/>
       <c r="D5" s="18"/>
-      <c r="E5" s="41"/>
-    </row>
-    <row r="6" spans="1:7">
+      <c r="E5" s="23"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="36"/>
+      <c r="B6" s="37"/>
       <c r="C6" s="17"/>
       <c r="D6" s="18"/>
-      <c r="E6" s="41"/>
-    </row>
-    <row r="7" spans="1:7">
+      <c r="E6" s="23"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="36"/>
+      <c r="B7" s="37"/>
       <c r="C7" s="17"/>
       <c r="D7" s="18"/>
-      <c r="E7" s="41"/>
-    </row>
-    <row r="8" spans="1:7">
+      <c r="E7" s="23"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="37" t="s">
+      <c r="B8" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="38"/>
-      <c r="D8" s="38"/>
-      <c r="E8" s="41"/>
-    </row>
-    <row r="9" spans="1:7" ht="30" customHeight="1">
+      <c r="C8" s="39"/>
+      <c r="D8" s="39"/>
+      <c r="E8" s="23"/>
+    </row>
+    <row r="9" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B9" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="23" t="s">
+      <c r="C9" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="D9" s="24"/>
-      <c r="E9" s="41"/>
-    </row>
-    <row r="10" spans="1:7" ht="30" customHeight="1">
+      <c r="D9" s="44"/>
+      <c r="E9" s="23"/>
+    </row>
+    <row r="10" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
         <v>18</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="23" t="s">
+      <c r="C10" s="43" t="s">
         <v>20</v>
       </c>
-      <c r="D10" s="24"/>
-      <c r="E10" s="41"/>
-    </row>
-    <row r="11" spans="1:7" ht="30" customHeight="1">
+      <c r="D10" s="44"/>
+      <c r="E10" s="23"/>
+    </row>
+    <row r="11" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
         <v>21</v>
       </c>
       <c r="B11" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="23" t="s">
+      <c r="C11" s="43" t="s">
         <v>23</v>
       </c>
-      <c r="D11" s="24"/>
-      <c r="E11" s="41"/>
-    </row>
-    <row r="12" spans="1:7" ht="30" customHeight="1">
+      <c r="D11" s="44"/>
+      <c r="E11" s="23"/>
+    </row>
+    <row r="12" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
         <v>24</v>
       </c>
       <c r="B12" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="C12" s="23" t="s">
+      <c r="C12" s="43" t="s">
         <v>26</v>
       </c>
-      <c r="D12" s="24"/>
-      <c r="E12" s="41"/>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13" s="43" t="s">
+      <c r="D12" s="44"/>
+      <c r="E12" s="23"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A13" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="B13" s="44" t="s">
+      <c r="B13" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="C13" s="44"/>
-      <c r="D13" s="44"/>
-      <c r="E13" s="41"/>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" s="43"/>
-      <c r="B14" s="44"/>
-      <c r="C14" s="44"/>
-      <c r="D14" s="44"/>
-      <c r="E14" s="41"/>
-    </row>
-    <row r="15" spans="1:7">
+      <c r="C13" s="26"/>
+      <c r="D13" s="26"/>
+      <c r="E13" s="23"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A14" s="25"/>
+      <c r="B14" s="26"/>
+      <c r="C14" s="26"/>
+      <c r="D14" s="26"/>
+      <c r="E14" s="23"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B15" s="39" t="s">
+      <c r="B15" s="40" t="s">
         <v>30</v>
       </c>
       <c r="C15" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="D15" s="27" t="s">
+      <c r="D15" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="E15" s="41"/>
-    </row>
-    <row r="16" spans="1:7">
+      <c r="E15" s="23"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B16" s="39"/>
+      <c r="B16" s="40"/>
       <c r="C16" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="D16" s="28"/>
-      <c r="E16" s="41"/>
-    </row>
-    <row r="17" spans="1:5">
+      <c r="D16" s="29"/>
+      <c r="E16" s="23"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B17" s="39"/>
+      <c r="B17" s="40"/>
       <c r="C17" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="D17" s="28"/>
-      <c r="E17" s="41"/>
-    </row>
-    <row r="18" spans="1:5">
+      <c r="D17" s="29"/>
+      <c r="E17" s="23"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B18" s="39"/>
-      <c r="C18" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="D18" s="28"/>
-      <c r="E18" s="41"/>
-    </row>
-    <row r="19" spans="1:5">
+      <c r="B18" s="40"/>
+      <c r="C18" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="D18" s="29"/>
+      <c r="E18" s="23"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="20" t="s">
+      <c r="B19" s="27" t="s">
         <v>40</v>
       </c>
       <c r="C19" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="D19" s="29"/>
+      <c r="E19" s="23"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A20" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D19" s="28"/>
-      <c r="E19" s="41"/>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="B20" s="27"/>
+      <c r="C20" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="B20" s="20"/>
-      <c r="C20" s="14" t="s">
+      <c r="D20" s="29"/>
+      <c r="E20" s="23"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A21" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D20" s="28"/>
-      <c r="E20" s="41"/>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="B21" s="27" t="s">
         <v>44</v>
-      </c>
-      <c r="B21" s="20" t="s">
-        <v>45</v>
       </c>
       <c r="C21" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="D21" s="28"/>
-      <c r="E21" s="41"/>
-    </row>
-    <row r="22" spans="1:5">
+      <c r="D21" s="29"/>
+      <c r="E21" s="23"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B22" s="27"/>
+      <c r="C22" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="D22" s="29"/>
+      <c r="E22" s="23"/>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A23" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="B22" s="20"/>
-      <c r="C22" s="13" t="s">
+      <c r="B23" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="D22" s="28"/>
-      <c r="E22" s="41"/>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="B23" s="16" t="s">
+      <c r="C23" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="D23" s="30"/>
+      <c r="E23" s="23"/>
+    </row>
+    <row r="24" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="C23" s="15" t="s">
+      <c r="B24" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="D23" s="29"/>
-      <c r="E23" s="41"/>
-    </row>
-    <row r="24" spans="1:5" ht="15.75" thickBot="1">
-      <c r="A24" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B24" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="C24" s="25"/>
-      <c r="D24" s="26"/>
-      <c r="E24" s="42"/>
+      <c r="C24" s="15"/>
+      <c r="D24" s="21"/>
+      <c r="E24" s="24"/>
+    </row>
+    <row r="25" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C25" s="20"/>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="15">
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
     <mergeCell ref="E2:E24"/>
     <mergeCell ref="A13:A14"/>
     <mergeCell ref="B13:D14"/>
     <mergeCell ref="B19:B20"/>
-    <mergeCell ref="C24:D24"/>
     <mergeCell ref="D15:D23"/>
     <mergeCell ref="B2:D4"/>
     <mergeCell ref="B5:B7"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="B15:B18"/>
     <mergeCell ref="B21:B22"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1326,7 +1322,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC73D3FB-3DF3-46AD-A52E-7806E9475FC7}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1335,7 +1331,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A7EC007-7AC0-4AB6-AAB7-DDECB3EF96E1}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
